--- a/templates/commercial_invoice.xlsx
+++ b/templates/commercial_invoice.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rotork-my.sharepoint.com/personal/jeongtaek_bang_rotork_com/Documents/바탕 화면/업무/NOAH ACTUATION/noahAutomation/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="148" documentId="11_482B29FEF0C7F80AEE82E0F7E4E761DFCF1F255D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB4EB15B-8992-4B0E-8BF7-A5E673058211}"/>
+  <xr:revisionPtr revIDLastSave="158" documentId="11_482B29FEF0C7F80AEE82E0F7E4E761DFCF1F255D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50C34FE2-502D-4EEA-8FB6-0A743EB0D523}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Table 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Table 1'!$A$1:$I$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Table 1'!$A$1:$I$49</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Table 1'!$1:$18</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -194,10 +194,11 @@
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>HS CODE</t>
-  </si>
-  <si>
-    <t/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -473,17 +474,6 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="medium">
         <color auto="1"/>
       </top>
@@ -538,6 +528,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -546,7 +545,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -592,9 +591,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="3" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -618,9 +614,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -644,15 +637,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -662,90 +646,69 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
@@ -757,73 +720,88 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1238,31 +1216,31 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.5" style="31" customWidth="1"/>
-    <col min="2" max="2" width="5.6640625" style="31" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" style="31" customWidth="1"/>
-    <col min="4" max="4" width="14.5" style="31" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" style="31" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" style="31" customWidth="1"/>
-    <col min="7" max="7" width="13.83203125" style="31" customWidth="1"/>
-    <col min="8" max="8" width="11.1640625" style="31" customWidth="1"/>
-    <col min="9" max="9" width="21.83203125" style="31" customWidth="1"/>
-    <col min="10" max="10" width="14" style="31" customWidth="1"/>
+    <col min="1" max="1" width="10.5" style="29" customWidth="1"/>
+    <col min="2" max="2" width="5.6640625" style="29" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" style="29" customWidth="1"/>
+    <col min="4" max="4" width="14.5" style="29" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" style="29" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" style="29" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" style="29" customWidth="1"/>
+    <col min="8" max="8" width="11.1640625" style="29" customWidth="1"/>
+    <col min="9" max="9" width="21.83203125" style="29" customWidth="1"/>
+    <col min="10" max="10" width="14" style="29" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="86"/>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
+      <c r="A1" s="38"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
       <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1270,12 +1248,12 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
-      <c r="E2" s="88" t="s">
+      <c r="E2" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
     </row>
@@ -1292,242 +1270,242 @@
       <c r="J3" s="2"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="52"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="22" t="s">
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="21"/>
+      <c r="G4" s="20"/>
       <c r="H4" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="21"/>
+      <c r="I4" s="20"/>
       <c r="J4" s="1"/>
     </row>
     <row r="5" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="67" t="s">
+      <c r="A5" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="32" t="s">
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="G5" s="17"/>
+      <c r="G5" s="16"/>
       <c r="H5" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="I5" s="17"/>
+      <c r="I5" s="16"/>
       <c r="J5" s="1"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="70"/>
-      <c r="B6" s="68"/>
-      <c r="C6" s="68"/>
-      <c r="D6" s="68"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="63" t="s">
+      <c r="A6" s="81"/>
+      <c r="B6" s="79"/>
+      <c r="C6" s="79"/>
+      <c r="D6" s="79"/>
+      <c r="E6" s="80"/>
+      <c r="F6" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="53"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="46"/>
       <c r="J6" s="1"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" s="71"/>
-      <c r="B7" s="72"/>
-      <c r="C7" s="72"/>
-      <c r="D7" s="72"/>
-      <c r="E7" s="73"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="55"/>
+      <c r="A7" s="82"/>
+      <c r="B7" s="83"/>
+      <c r="C7" s="83"/>
+      <c r="D7" s="83"/>
+      <c r="E7" s="84"/>
+      <c r="F7" s="73"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="66"/>
       <c r="J7" s="1"/>
     </row>
     <row r="8" spans="1:10" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="51" t="s">
+      <c r="A8" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="56"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49"/>
-      <c r="I8" s="55"/>
+      <c r="B8" s="45"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="74"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="66"/>
       <c r="J8" s="1"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" s="67"/>
-      <c r="B9" s="93"/>
-      <c r="C9" s="93"/>
-      <c r="D9" s="93"/>
-      <c r="E9" s="94"/>
-      <c r="F9" s="56"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="55"/>
+      <c r="A9" s="52"/>
+      <c r="B9" s="53"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="74"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="66"/>
       <c r="J9" s="4"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" s="67"/>
-      <c r="B10" s="93"/>
-      <c r="C10" s="93"/>
-      <c r="D10" s="93"/>
-      <c r="E10" s="94"/>
-      <c r="F10" s="56"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="55"/>
+      <c r="A10" s="52"/>
+      <c r="B10" s="53"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="53"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="74"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="66"/>
       <c r="J10" s="4"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" s="95"/>
-      <c r="B11" s="96"/>
-      <c r="C11" s="96"/>
-      <c r="D11" s="96"/>
-      <c r="E11" s="97"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="58"/>
-      <c r="H11" s="58"/>
-      <c r="I11" s="59"/>
+      <c r="A11" s="55"/>
+      <c r="B11" s="56"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="56"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="75"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="41"/>
       <c r="J11" s="2"/>
     </row>
     <row r="12" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="51" t="s">
+      <c r="A12" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="52"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="63" t="s">
+      <c r="B12" s="45"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="53"/>
-      <c r="H12" s="62"/>
-      <c r="I12" s="60"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="76"/>
       <c r="J12" s="2"/>
     </row>
     <row r="13" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="90"/>
-      <c r="B13" s="58"/>
-      <c r="C13" s="58"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="59"/>
-      <c r="F13" s="56"/>
-      <c r="G13" s="55"/>
-      <c r="H13" s="49"/>
-      <c r="I13" s="55"/>
+      <c r="A13" s="47"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="74"/>
+      <c r="G13" s="66"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="66"/>
       <c r="J13" s="2"/>
     </row>
     <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="77" t="s">
+      <c r="B14" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="66"/>
-      <c r="D14" s="66"/>
-      <c r="E14" s="76"/>
-      <c r="F14" s="79" t="s">
+      <c r="C14" s="64"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="55"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="55"/>
+      <c r="G14" s="66"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="66"/>
       <c r="J14" s="2"/>
     </row>
     <row r="15" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="77"/>
-      <c r="C15" s="66"/>
-      <c r="D15" s="66"/>
-      <c r="E15" s="76"/>
-      <c r="F15" s="87" t="s">
+      <c r="B15" s="63"/>
+      <c r="C15" s="64"/>
+      <c r="D15" s="64"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="G15" s="59"/>
-      <c r="H15" s="58"/>
-      <c r="I15" s="59"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="41"/>
       <c r="J15" s="2"/>
     </row>
     <row r="16" spans="1:10" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="80" t="s">
+      <c r="A16" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="66"/>
-      <c r="C16" s="66"/>
-      <c r="D16" s="75"/>
-      <c r="E16" s="76"/>
-      <c r="F16" s="16" t="s">
+      <c r="B16" s="64"/>
+      <c r="C16" s="64"/>
+      <c r="D16" s="61"/>
+      <c r="E16" s="62"/>
+      <c r="F16" s="15" t="s">
         <v>15</v>
       </c>
       <c r="G16" s="12"/>
       <c r="H16" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="I16" s="19"/>
+      <c r="I16" s="18"/>
       <c r="J16" s="1"/>
     </row>
     <row r="17" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="25"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="27"/>
+      <c r="A17" s="23"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="25"/>
       <c r="G17" s="7"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="29"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="27"/>
       <c r="J17" s="1"/>
     </row>
     <row r="18" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="65" t="s">
+      <c r="A18" s="58" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="65"/>
-      <c r="C18" s="65"/>
-      <c r="D18" s="98" t="s">
-        <v>47</v>
-      </c>
-      <c r="E18" s="37" t="s">
+      <c r="B18" s="58"/>
+      <c r="C18" s="58"/>
+      <c r="D18" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="F18" s="36" t="s">
+      <c r="F18" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="G18" s="36" t="s">
+      <c r="G18" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="H18" s="38" t="s">
+      <c r="H18" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="I18" s="36" t="s">
+      <c r="I18" s="31" t="s">
         <v>20</v>
       </c>
       <c r="J18" s="6"/>
     </row>
     <row r="19" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="81" t="s">
+      <c r="A19" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="81"/>
-      <c r="C19" s="81"/>
-      <c r="D19" s="45"/>
+      <c r="B19" s="59"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="34"/>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
       <c r="G19" s="3"/>
@@ -1536,292 +1514,292 @@
       <c r="J19" s="1"/>
     </row>
     <row r="20" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="61" t="s">
+      <c r="A20" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="61"/>
-      <c r="C20" s="61"/>
-      <c r="D20" s="99" t="s">
-        <v>48</v>
-      </c>
-      <c r="E20" s="46"/>
-      <c r="F20" s="39">
+      <c r="B20" s="85"/>
+      <c r="C20" s="85"/>
+      <c r="D20" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E20" s="37"/>
+      <c r="F20" s="86">
         <v>10</v>
       </c>
-      <c r="G20" s="42">
+      <c r="G20" s="87">
         <v>24</v>
       </c>
-      <c r="H20" s="34" t="s">
+      <c r="H20" s="88" t="s">
         <v>22</v>
       </c>
-      <c r="I20" s="44">
+      <c r="I20" s="89">
         <f t="shared" ref="I20:I27" si="0">E20*G20</f>
         <v>0</v>
       </c>
       <c r="J20" s="1"/>
     </row>
     <row r="21" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="61" t="s">
+      <c r="A21" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="61"/>
-      <c r="C21" s="61"/>
-      <c r="D21" s="99"/>
-      <c r="E21" s="46"/>
-      <c r="F21" s="39">
+      <c r="B21" s="85"/>
+      <c r="C21" s="85"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="86">
         <v>10</v>
       </c>
-      <c r="G21" s="42">
+      <c r="G21" s="87">
         <v>1.26</v>
       </c>
-      <c r="H21" s="34" t="s">
+      <c r="H21" s="88" t="s">
         <v>22</v>
       </c>
-      <c r="I21" s="44">
+      <c r="I21" s="89">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J21" s="1"/>
     </row>
     <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="61" t="s">
+      <c r="A22" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="61"/>
-      <c r="C22" s="61"/>
-      <c r="D22" s="99"/>
-      <c r="E22" s="46"/>
-      <c r="F22" s="39">
+      <c r="B22" s="85"/>
+      <c r="C22" s="85"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="86">
         <v>10</v>
       </c>
-      <c r="G22" s="42">
+      <c r="G22" s="87">
         <v>3.7</v>
       </c>
-      <c r="H22" s="34" t="s">
+      <c r="H22" s="88" t="s">
         <v>22</v>
       </c>
-      <c r="I22" s="44">
+      <c r="I22" s="89">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J22" s="1"/>
     </row>
     <row r="23" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="61" t="s">
+      <c r="A23" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="61"/>
-      <c r="C23" s="61"/>
-      <c r="D23" s="99"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="39">
+      <c r="B23" s="85"/>
+      <c r="C23" s="85"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="86">
         <v>10</v>
       </c>
-      <c r="G23" s="42">
+      <c r="G23" s="87">
         <v>3.9</v>
       </c>
-      <c r="H23" s="34" t="s">
+      <c r="H23" s="88" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="44">
+      <c r="I23" s="89">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J23" s="1"/>
     </row>
     <row r="24" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="61" t="s">
+      <c r="A24" s="85" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="61"/>
-      <c r="C24" s="61"/>
-      <c r="D24" s="99"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="39">
+      <c r="B24" s="85"/>
+      <c r="C24" s="85"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="86">
         <v>10</v>
       </c>
-      <c r="G24" s="42">
+      <c r="G24" s="87">
         <v>3.9</v>
       </c>
-      <c r="H24" s="34" t="s">
+      <c r="H24" s="88" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="44">
+      <c r="I24" s="89">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J24" s="1"/>
     </row>
     <row r="25" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="61" t="s">
+      <c r="A25" s="85" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="61"/>
-      <c r="C25" s="61"/>
-      <c r="D25" s="99"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="39">
+      <c r="B25" s="85"/>
+      <c r="C25" s="85"/>
+      <c r="D25" s="36"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="86">
         <v>10</v>
       </c>
-      <c r="G25" s="42">
+      <c r="G25" s="87">
         <v>2.5</v>
       </c>
-      <c r="H25" s="34" t="s">
+      <c r="H25" s="88" t="s">
         <v>22</v>
       </c>
-      <c r="I25" s="44">
+      <c r="I25" s="89">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J25" s="1"/>
     </row>
     <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="61" t="s">
+      <c r="A26" s="85" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="61"/>
-      <c r="C26" s="61"/>
-      <c r="D26" s="99"/>
-      <c r="E26" s="46"/>
-      <c r="F26" s="39">
+      <c r="B26" s="85"/>
+      <c r="C26" s="85"/>
+      <c r="D26" s="36"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="86">
         <v>10</v>
       </c>
-      <c r="G26" s="42">
+      <c r="G26" s="87">
         <v>2.9</v>
       </c>
-      <c r="H26" s="34" t="s">
+      <c r="H26" s="88" t="s">
         <v>22</v>
       </c>
-      <c r="I26" s="44">
+      <c r="I26" s="89">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J26" s="1"/>
     </row>
     <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="78" t="s">
+      <c r="A27" s="85" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="78"/>
-      <c r="C27" s="78"/>
-      <c r="D27" s="100"/>
-      <c r="E27" s="47"/>
-      <c r="F27" s="40">
+      <c r="B27" s="85"/>
+      <c r="C27" s="85"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="86">
         <v>10</v>
       </c>
-      <c r="G27" s="43">
+      <c r="G27" s="87">
         <v>2.9</v>
       </c>
-      <c r="H27" s="35" t="s">
+      <c r="H27" s="88" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="44">
+      <c r="I27" s="89">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J27" s="1"/>
     </row>
     <row r="28" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="89" t="s">
+      <c r="A28" s="90" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="89"/>
-      <c r="C28" s="89"/>
-      <c r="D28" s="101"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="41">
+      <c r="B28" s="90"/>
+      <c r="C28" s="90"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="91"/>
+      <c r="F28" s="92">
         <f>SUM(F20:F27)</f>
         <v>80</v>
       </c>
-      <c r="G28" s="33" t="s">
+      <c r="G28" s="93" t="s">
         <v>31</v>
       </c>
-      <c r="H28" s="33" t="s">
+      <c r="H28" s="93" t="s">
         <v>22</v>
       </c>
-      <c r="I28" s="24">
+      <c r="I28" s="94">
         <f>SUM(I20:I27)</f>
         <v>0</v>
       </c>
       <c r="J28" s="2"/>
     </row>
     <row r="29" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="91" t="s">
+      <c r="A29" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="92"/>
-      <c r="C29" s="92"/>
-      <c r="D29" s="92"/>
-      <c r="E29" s="92"/>
-      <c r="F29" s="92"/>
-      <c r="G29" s="92"/>
-      <c r="H29" s="92"/>
-      <c r="I29" s="92"/>
+      <c r="B29" s="50"/>
+      <c r="C29" s="50"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="50"/>
+      <c r="F29" s="50"/>
+      <c r="G29" s="50"/>
+      <c r="H29" s="50"/>
+      <c r="I29" s="50"/>
       <c r="J29" s="6"/>
     </row>
     <row r="30" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="20"/>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
+      <c r="A30" s="19"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
       <c r="J30" s="6"/>
     </row>
     <row r="31" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="82" t="s">
+      <c r="A31" s="68" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="49"/>
-      <c r="C31" s="49"/>
-      <c r="D31" s="49"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
+      <c r="B31" s="39"/>
+      <c r="C31" s="39"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
       <c r="J31" s="6"/>
     </row>
     <row r="32" spans="1:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="82" t="s">
+      <c r="A32" s="68" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="49"/>
-      <c r="C32" s="49"/>
-      <c r="D32" s="49"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
+      <c r="B32" s="39"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
       <c r="J32" s="6"/>
     </row>
     <row r="33" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="83" t="s">
+      <c r="A33" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="B33" s="84"/>
-      <c r="C33" s="84"/>
-      <c r="D33" s="84"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="20"/>
-      <c r="I33" s="20"/>
+      <c r="B33" s="70"/>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
       <c r="J33" s="6"/>
     </row>
     <row r="34" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="50" t="s">
+      <c r="A34" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="B34" s="49"/>
-      <c r="C34" s="50">
+      <c r="B34" s="39"/>
+      <c r="C34" s="43">
         <v>8116409</v>
       </c>
-      <c r="D34" s="49"/>
+      <c r="D34" s="39"/>
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
       <c r="G34" s="7"/>
@@ -1830,12 +1808,12 @@
       <c r="J34" s="8"/>
     </row>
     <row r="35" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="50" t="s">
+      <c r="A35" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="49"/>
-      <c r="C35" s="64"/>
-      <c r="D35" s="49"/>
+      <c r="B35" s="39"/>
+      <c r="C35" s="78"/>
+      <c r="D35" s="39"/>
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
       <c r="G35" s="7"/>
@@ -1844,12 +1822,12 @@
       <c r="J35" s="8"/>
     </row>
     <row r="36" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="50" t="s">
+      <c r="A36" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="49"/>
-      <c r="C36" s="82"/>
-      <c r="D36" s="49"/>
+      <c r="B36" s="39"/>
+      <c r="C36" s="68"/>
+      <c r="D36" s="39"/>
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
       <c r="G36" s="7"/>
@@ -1858,10 +1836,10 @@
       <c r="J36" s="8"/>
     </row>
     <row r="37" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="18"/>
-      <c r="B37" s="18"/>
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
+      <c r="A37" s="17"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
       <c r="G37" s="7"/>
@@ -1870,10 +1848,10 @@
       <c r="J37" s="8"/>
     </row>
     <row r="38" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="18"/>
-      <c r="B38" s="18"/>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
+      <c r="A38" s="17"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
       <c r="G38" s="7"/>
@@ -1882,10 +1860,10 @@
       <c r="J38" s="8"/>
     </row>
     <row r="39" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="18"/>
-      <c r="B39" s="18"/>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
+      <c r="A39" s="17"/>
+      <c r="B39" s="17"/>
+      <c r="C39" s="17"/>
+      <c r="D39" s="17"/>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
       <c r="G39" s="7"/>
@@ -1894,10 +1872,10 @@
       <c r="J39" s="8"/>
     </row>
     <row r="40" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="18"/>
-      <c r="B40" s="18"/>
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
+      <c r="A40" s="17"/>
+      <c r="B40" s="17"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="17"/>
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
       <c r="G40" s="7"/>
@@ -1905,46 +1883,151 @@
       <c r="I40" s="7"/>
       <c r="J40" s="8"/>
     </row>
-    <row r="41" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="48" t="s">
+    <row r="41" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="17"/>
+      <c r="B41" s="17"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
+      <c r="H41" s="7"/>
+      <c r="I41" s="7"/>
+      <c r="J41" s="8"/>
+    </row>
+    <row r="42" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="17"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7"/>
+      <c r="H42" s="7"/>
+      <c r="I42" s="7"/>
+      <c r="J42" s="8"/>
+    </row>
+    <row r="43" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="17"/>
+      <c r="B43" s="17"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="17"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="7"/>
+      <c r="H43" s="7"/>
+      <c r="I43" s="7"/>
+      <c r="J43" s="8"/>
+    </row>
+    <row r="44" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="17"/>
+      <c r="B44" s="17"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="7"/>
+      <c r="G44" s="7"/>
+      <c r="H44" s="7"/>
+      <c r="I44" s="7"/>
+      <c r="J44" s="8"/>
+    </row>
+    <row r="45" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="17"/>
+      <c r="B45" s="17"/>
+      <c r="C45" s="17"/>
+      <c r="D45" s="17"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="7"/>
+      <c r="H45" s="7"/>
+      <c r="I45" s="7"/>
+      <c r="J45" s="8"/>
+    </row>
+    <row r="46" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="17"/>
+      <c r="B46" s="17"/>
+      <c r="C46" s="17"/>
+      <c r="D46" s="17"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="7"/>
+      <c r="G46" s="7"/>
+      <c r="H46" s="7"/>
+      <c r="I46" s="7"/>
+      <c r="J46" s="8"/>
+    </row>
+    <row r="47" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="17"/>
+      <c r="B47" s="17"/>
+      <c r="C47" s="17"/>
+      <c r="D47" s="17"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="7"/>
+      <c r="H47" s="7"/>
+      <c r="I47" s="7"/>
+      <c r="J47" s="8"/>
+    </row>
+    <row r="48" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="72" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="49"/>
-      <c r="C41" s="49"/>
-      <c r="D41" s="49"/>
-      <c r="E41" s="49"/>
-      <c r="F41" s="49"/>
-      <c r="G41" s="49"/>
-      <c r="H41" s="49"/>
-      <c r="I41" s="49"/>
-      <c r="J41" s="8"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A42" s="85" t="s">
+      <c r="B48" s="39"/>
+      <c r="C48" s="39"/>
+      <c r="D48" s="39"/>
+      <c r="E48" s="39"/>
+      <c r="F48" s="39"/>
+      <c r="G48" s="39"/>
+      <c r="H48" s="39"/>
+      <c r="I48" s="39"/>
+      <c r="J48" s="8"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A49" s="71" t="s">
         <v>39</v>
       </c>
-      <c r="B42" s="49"/>
-      <c r="C42" s="49"/>
-      <c r="D42" s="49"/>
-      <c r="E42" s="49"/>
-      <c r="F42" s="74" t="s">
+      <c r="B49" s="39"/>
+      <c r="C49" s="39"/>
+      <c r="D49" s="39"/>
+      <c r="E49" s="39"/>
+      <c r="F49" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="G42" s="49"/>
-      <c r="H42" s="49"/>
-      <c r="I42" s="49"/>
-      <c r="J42" s="9"/>
+      <c r="G49" s="39"/>
+      <c r="H49" s="39"/>
+      <c r="I49" s="39"/>
+      <c r="J49" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="F7:I11"/>
+    <mergeCell ref="I12:I15"/>
+    <mergeCell ref="H12:H15"/>
+    <mergeCell ref="F12:G13"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="A5:E7"/>
+    <mergeCell ref="A20:C20"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="A25:C25"/>
+    <mergeCell ref="F49:I49"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A48:I48"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:C28"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="F15:G15"/>
     <mergeCell ref="E2:H2"/>
@@ -1960,35 +2043,14 @@
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A19:C19"/>
-    <mergeCell ref="F42:I42"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="A41:I41"/>
-    <mergeCell ref="A36:B36"/>
     <mergeCell ref="A12:E12"/>
-    <mergeCell ref="F7:I11"/>
-    <mergeCell ref="I12:I15"/>
-    <mergeCell ref="H12:H15"/>
-    <mergeCell ref="F12:G13"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="A5:E7"/>
-    <mergeCell ref="A20:C20"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F42" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="F49" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.39370078740157483" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="89" fitToHeight="0" orientation="portrait" r:id="rId2"/>
   <headerFooter>
     <oddFooter>Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
